--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 8,16</t>
+          <t>2,94; 8,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 9,62</t>
+          <t>4,21; 9,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,7</t>
+          <t>2,72; 9,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60,4; 297,97</t>
+          <t>59,22; 314,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>101,86; 424,49</t>
+          <t>85,03; 402,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,37; 132,29</t>
+          <t>26,72; 125,72</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,63</t>
+          <t>3,38; 7,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,52</t>
+          <t>3,28; 7,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 12,81</t>
+          <t>6,75; 12,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,71; 305,42</t>
+          <t>77,1; 306,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,63; 336,54</t>
+          <t>89,11; 348,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>101,6; 420,2</t>
+          <t>93,26; 406,78</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,87</t>
+          <t>2,05; 7,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,38</t>
+          <t>2,5; 7,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 7,26</t>
+          <t>-2,07; 7,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,76; 255,03</t>
+          <t>34,24; 254,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71,36; 393,84</t>
+          <t>58,57; 338,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 126,62</t>
+          <t>-26,15; 126,1</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,19</t>
+          <t>4,57; 9,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,71</t>
+          <t>3,99; 8,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 11,52</t>
+          <t>5,57; 11,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,82; 325,33</t>
+          <t>93,65; 361,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,86; 326,58</t>
+          <t>86,51; 356,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,15; 202,14</t>
+          <t>76,08; 200,89</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,86</t>
+          <t>4,57; 6,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,03</t>
+          <t>4,72; 7,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,97</t>
+          <t>4,63; 9,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111,2; 217,98</t>
+          <t>113,53; 227,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>132,22; 256,47</t>
+          <t>131,62; 257,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,6; 159,89</t>
+          <t>68,95; 162,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_5-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_5-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,68</t>
+          <t>7,75</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,34</t>
+          <t>2,72; 8,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,78</t>
+          <t>4,01; 9,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 9,6</t>
+          <t>4,96; 10,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59,22; 314,76</t>
+          <t>55,49; 296,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,03; 402,95</t>
+          <t>92,71; 409,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,72; 125,72</t>
+          <t>46,55; 137,55</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9,21</t>
+          <t>7,75</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>173,3%</t>
+          <t>120,58%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 7,83</t>
+          <t>3,31; 7,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,62</t>
+          <t>3,04; 7,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 12,83</t>
+          <t>5,45; 9,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,1; 306,01</t>
+          <t>74,7; 293,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>89,11; 348,02</t>
+          <t>78,19; 317,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,26; 406,78</t>
+          <t>71,0; 177,88</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>6,58</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>103,95%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,14</t>
+          <t>2,09; 6,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,21</t>
+          <t>2,7; 7,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 7,44</t>
+          <t>3,83; 9,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,24; 254,96</t>
+          <t>42,1; 260,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,57; 338,13</t>
+          <t>67,98; 382,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 126,1</t>
+          <t>50,67; 187,23</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,86</t>
+          <t>9,55</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>128,71%</t>
+          <t>140,24%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,44</t>
+          <t>4,62; 9,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,96</t>
+          <t>4,01; 8,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 11,9</t>
+          <t>7,12; 11,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93,65; 361,29</t>
+          <t>97,24; 336,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,51; 356,48</t>
+          <t>92,47; 332,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,08; 200,89</t>
+          <t>87,42; 202,48</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>8,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>109,25%</t>
+          <t>115,23%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 6,87</t>
+          <t>4,52; 7,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 7,08</t>
+          <t>4,67; 7,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,63; 9,09</t>
+          <t>6,76; 9,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113,53; 227,32</t>
+          <t>108,48; 224,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>131,62; 257,54</t>
+          <t>132,91; 263,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,95; 162,33</t>
+          <t>88,99; 146,03</t>
         </is>
       </c>
     </row>
